--- a/Optimization of scientific outcomes reporting/Prawosławne Seminarium Duchowne w Warszawie/Evaluation optimize penalties k.xlsx
+++ b/Optimization of scientific outcomes reporting/Prawosławne Seminarium Duchowne w Warszawie/Evaluation optimize penalties k.xlsx
@@ -30,14 +30,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Statystyki!$A$3:$Y$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">'802pub'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">'802pat'!$A$2:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="true">'802os'!$A$2:$T$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="true">'802ospat'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="true">'802osproj'!$A$2:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="true">OśwDyscypliny!$A$1:$L$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="true">OśwOsiągnięcia!$A$1:$V$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="true">Nieewaluowani!$A$2:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="true">Konfiguracja!$A$1:$D$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="true">Osoby!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="true">'802os'!$A$2:$V$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="true">'802ospat'!$A$2:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="true">'802osproj'!$A$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="true">OśwDyscypliny!$A$1:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="true">OśwOsiągnięcia!$A$1:$Y$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="true">Nieewaluowani!$A$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="true">Konfiguracja!$A$1:$E$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="true">Osoby!$A$1:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="true">'Inne zatrudnienie'!$A$2:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="true">Dyscypliny!$A$1:$K$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="true">Publikacje!$A$1:$S$1</definedName>
@@ -213,17 +213,17 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="B17" authorId="0">
+    <comment ref="B15" authorId="0">
       <text>
         <t>§17 ust. 1</t>
       </text>
     </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <t>§17 ust. 5-7</t>
+      </text>
+    </comment>
     <comment ref="B18" authorId="0">
-      <text>
-        <t>§17 ust. 5-7</t>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0">
       <text>
         <t>Opcja uniemożliwia zmianę dyscypliny dla udziału autora w publikacji</t>
       </text>
@@ -243,97 +243,102 @@
         <t>UUID w systemie POL-on lub inny identyfikator</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>UUID w systemie POL-on lub inny identyfikator</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <t>§17 ust. 1-4</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <t>§11 ust. 1 p. 1)</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <t>§11 ust. 1 p. 2)</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <t>§11 ust. 1 p. 3)</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <t>§17 ust. 10</t>
       </text>
     </comment>
-    <comment ref="G2" authorId="0">
+    <comment ref="H2" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G7" authorId="0">
+    <comment ref="H7" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G8" authorId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G9" authorId="0">
+    <comment ref="H9" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G10" authorId="0">
+    <comment ref="H10" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G11" authorId="0">
+    <comment ref="H11" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0">
+    <comment ref="H12" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0">
+    <comment ref="H13" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G14" authorId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
     </comment>
-    <comment ref="G15" authorId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <t>2022, 2023, 2024, 2025</t>
       </text>
@@ -413,6 +418,11 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>PBN Id lub inny identyfikator</t>
+      </text>
+    </comment>
     <comment ref="M1" authorId="0">
       <text>
         <t>Min po dyscyplinach z całkowitej wartości punktowej (§12)</t>
@@ -609,6 +619,11 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="A2" authorId="0">
+      <text>
+        <t>PBN Id lub inny identyfikator</t>
+      </text>
+    </comment>
     <comment ref="D2" authorId="0">
       <text>
         <t>§12</t>
@@ -679,72 +694,87 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="A2" authorId="0">
+      <text>
+        <t>UUID w systemie POLon lub inny identyfikator</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0">
+      <text>
+        <t>UUID w systemie POLon lub inny identyfikator</t>
+      </text>
+    </comment>
     <comment ref="D2" authorId="0">
       <text>
+        <t>Ewaluowany jako pracownik w N, doktorant, lub pracownik poza N (§11 ust. 1)</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0">
+      <text>
         <t>Suma wartości punktowych udziałów w publikacjach (§16 ust. 4)</t>
       </text>
     </comment>
-    <comment ref="E2" authorId="0">
+    <comment ref="G2" authorId="0">
       <text>
         <t>Suma wartości punktowych udziałów w publikacjach za 140+ punktów (§16 ust. 4)</t>
       </text>
     </comment>
-    <comment ref="F2" authorId="0">
+    <comment ref="H2" authorId="0">
       <text>
         <t>Suma całkowitych wartości punktowych w publikacjach (§12)</t>
       </text>
     </comment>
-    <comment ref="G2" authorId="0">
+    <comment ref="I2" authorId="0">
       <text>
         <t>Suma udziałów w publikacjach (§16 ust. 2, 17 ust. 1)</t>
       </text>
     </comment>
-    <comment ref="H2" authorId="0">
+    <comment ref="J2" authorId="0">
       <text>
         <t>Limit udziałów w publikacjach (§17 ust. 1) - wg wyników optymalizacji oświadczeń o dyscyplinach</t>
       </text>
     </comment>
-    <comment ref="I2" authorId="0">
+    <comment ref="K2" authorId="0">
       <text>
         <t>Limit udziałów w publikacjach (§17 ust. 1) - wg stanu bazowego w POLon</t>
       </text>
     </comment>
-    <comment ref="K2" authorId="0">
+    <comment ref="M2" authorId="0">
       <text>
         <t>Udział w liczbie N (§7, §11 ust. 1)</t>
       </text>
     </comment>
-    <comment ref="L2" authorId="0">
+    <comment ref="N2" authorId="0">
       <text>
         <t>Udział w liczbie N (§7, §11 ust. 1)</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
+    <comment ref="O2" authorId="0">
       <text>
         <t>Niewykorzystane przez tę osobę punkty w publikacjach przyjmując k=max(k). Inni autorzy mogą wykorzystać część z tych punktów.</t>
       </text>
     </comment>
-    <comment ref="N2" authorId="0">
+    <comment ref="P2" authorId="0">
       <text>
         <t>Niewykorzystane przez tę osobę udziały w publikacjach przyjmując k=max(k). Inni autorzy mogą wykorzystać część z tych udziałów.</t>
       </text>
     </comment>
-    <comment ref="P2" authorId="0">
+    <comment ref="R2" authorId="0">
       <text>
         <t>§17 ust. 8 p. 1)</t>
       </text>
     </comment>
-    <comment ref="Q2" authorId="0">
+    <comment ref="S2" authorId="0">
       <text>
         <t>§17 ust. 8 p. 2)</t>
       </text>
     </comment>
-    <comment ref="R2" authorId="0">
+    <comment ref="T2" authorId="0">
       <text>
         <t>§17 ust. 9</t>
       </text>
     </comment>
-    <comment ref="S2" authorId="0">
+    <comment ref="U2" authorId="0">
       <text>
         <t>§17 ust. 10</t>
       </text>
@@ -761,10 +791,15 @@
   <commentList>
     <comment ref="D2" authorId="0">
       <text>
+        <t>§11 ust. 1</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0">
+      <text>
         <t>§19</t>
       </text>
     </comment>
-    <comment ref="E2" authorId="0">
+    <comment ref="G2" authorId="0">
       <text>
         <t>§19</t>
       </text>
@@ -779,7 +814,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0">
+    <comment ref="E2" authorId="0">
       <text>
         <t>§22</t>
       </text>
@@ -799,6 +834,11 @@
         <t>UUID w systemie POL-on lub inny identyfikator</t>
       </text>
     </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>UUID w systemie POL-on lub inny identyfikator</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -814,12 +854,22 @@
         <t>UUID w systemie POL-on lub inny identyfikator</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>UUID w systemie POL-on lub inny identyfikator</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <t>PBN Id lub inny identyfikator osiągnięcia</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
       <text>
         <t>Określa czy udział co najmniej jednego autora osiągnięcia wlicza się do finalnej oceny</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="Y1" authorId="0">
       <text>
         <t>Określa czy co najmniej jeden autor publikacji ma dyscyplinę nauki teologiczne jako optymalną lub w źródle danych.</t>
       </text>
@@ -834,22 +884,22 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0">
+    <comment ref="E2" authorId="0">
       <text>
         <t>nauki teologiczne: Suma całkowitych wartości punktowych w publikacjach (§12)</t>
       </text>
     </comment>
-    <comment ref="E2" authorId="0">
+    <comment ref="F2" authorId="0">
       <text>
         <t>nauki teologiczne: Suma wartości punktowych udziałów w publikacjach (§16 ust. 4)</t>
       </text>
     </comment>
-    <comment ref="F2" authorId="0">
+    <comment ref="G2" authorId="0">
       <text>
         <t>nauki teologiczne: Suma udziałów w publikacjach (§16 ust. 2, 17 ust. 1)</t>
       </text>
     </comment>
-    <comment ref="G2" authorId="0">
+    <comment ref="H2" authorId="0">
       <text>
         <t>§17 ust. 10</t>
       </text>
@@ -859,7 +909,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="368">
   <si>
     <t>Status</t>
   </si>
@@ -948,7 +998,7 @@
     <t>nauki teologiczne</t>
   </si>
   <si>
-    <t>id</t>
+    <t>Id</t>
   </si>
   <si>
     <t>Tytuł</t>
@@ -987,6 +1037,12 @@
     <t>Punkty w użyciu</t>
   </si>
   <si>
+    <t>Id pracownika</t>
+  </si>
+  <si>
+    <t>Id doktoranta</t>
+  </si>
+  <si>
     <t>Osoba</t>
   </si>
   <si>
@@ -1038,6 +1094,9 @@
     <t>Artur Aleksiejuk</t>
   </si>
   <si>
+    <t>Pracownik w N</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -1128,9 +1187,6 @@
     <t>∑pkt</t>
   </si>
   <si>
-    <t>Id osoby</t>
-  </si>
-  <si>
     <t>Imię</t>
   </si>
   <si>
@@ -1278,6 +1334,9 @@
     <t>U</t>
   </si>
   <si>
+    <t>Rola</t>
+  </si>
+  <si>
     <t>Dyscyplina w źródle danych</t>
   </si>
   <si>
@@ -1287,7 +1346,7 @@
     <t>Dotyczy nauki teologiczne</t>
   </si>
   <si>
-    <t>Dydaktycy</t>
+    <t>Nieewaluowani</t>
   </si>
   <si>
     <t>∑Pc 802</t>
@@ -1314,7 +1373,7 @@
     <t>Wersja rozporządzenia</t>
   </si>
   <si>
-    <t>V20211019</t>
+    <t>V20250730</t>
   </si>
   <si>
     <t>Rok ewaluacji</t>
@@ -1359,15 +1418,6 @@
     <t>Elastyczne k</t>
   </si>
   <si>
-    <t>Typ slotów</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Stosuj sloty dla dyscypliny</t>
-  </si>
-  <si>
     <t>Stosuj ograniczenia dla osób</t>
   </si>
   <si>
@@ -1590,9 +1640,6 @@
     <t>Progi dyskontowe dla oceny poziomu naukowego (§21) dla dyscypliny sztuki plastyczne i konserwacja dzieł sztuki</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>Indywidualny limit</t>
   </si>
   <si>
@@ -1602,7 +1649,7 @@
     <t>Zaliczony do N w dowolnym roku</t>
   </si>
   <si>
-    <t>Doktorant ze szkoły doktorskiej bez N</t>
+    <t xml:space="preserve">Doktorant ze szkoły doktorskiej </t>
   </si>
   <si>
     <t>Naukowy niezaliczony do N w dowolnym roku</t>
@@ -2333,7 +2380,7 @@
     <tabColor indexed="48"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="78.125" customWidth="true" bestFit="true"/>
@@ -2342,31 +2389,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>2022.0</v>
@@ -2374,7 +2421,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>2023.0</v>
@@ -2382,7 +2429,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>2024.0</v>
@@ -2390,7 +2437,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>2025.0</v>
@@ -2398,55 +2445,55 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" t="b" s="0">
         <v>1</v>
@@ -2454,119 +2501,119 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="B15" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B16" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B19" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B20" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="B21" t="b" s="0">
-        <v>1</v>
+        <v>175</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>176</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="B22" t="b" s="0">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="B23" t="n" s="0">
+        <v>25.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>177</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="B24" t="n" s="0">
+        <v>10000.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>25.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>179</v>
-      </c>
-      <c r="B26" t="n" s="0">
-        <v>10000.0</v>
+        <v>181</v>
+      </c>
+      <c r="B26" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>600.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="B28" t="b" s="0">
-        <v>1</v>
+        <v>183</v>
+      </c>
+      <c r="B28" t="n" s="0">
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>4.0</v>
@@ -2574,819 +2621,971 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>184</v>
-      </c>
-      <c r="B31" t="n" s="0">
-        <v>4.0</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>0.75</v>
+        <v>390.6608</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>429.94239999999996</v>
+      </c>
+      <c r="D32" t="n" s="0">
+        <v>469.22399999999993</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>508.50559999999996</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>186</v>
+        <v>188</v>
+      </c>
+      <c r="B33" t="n" s="0">
+        <v>270.6591</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>300.7098</v>
+      </c>
+      <c r="D33" t="n" s="0">
+        <v>330.7605</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>360.81120000000004</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>390.6608</v>
+        <v>259.4765</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>429.94239999999996</v>
+        <v>288.667</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>469.22399999999993</v>
+        <v>317.8575</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>347.048</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>270.6591</v>
+        <v>290.319</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>300.7098</v>
+        <v>321.88199999999995</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>330.7605</v>
+        <v>353.445</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>385.00800000000004</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>259.4765</v>
+        <v>277.77660000000003</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>288.667</v>
+        <v>308.3748</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>317.8575</v>
+        <v>338.973</v>
+      </c>
+      <c r="E36" t="n" s="0">
+        <v>369.57120000000003</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>290.319</v>
+        <v>260.45799999999997</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>321.88199999999995</v>
+        <v>289.724</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>353.445</v>
+        <v>318.99</v>
+      </c>
+      <c r="E37" t="n" s="0">
+        <v>348.25600000000003</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>277.77660000000003</v>
+        <v>267.9928</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>308.3748</v>
+        <v>297.8384</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>338.973</v>
+        <v>327.68399999999997</v>
+      </c>
+      <c r="E38" t="n" s="0">
+        <v>357.5296</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>260.45799999999997</v>
+        <v>277.9287</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>289.724</v>
+        <v>308.5386</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>318.99</v>
+        <v>339.1485</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>369.7584</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>267.9928</v>
+        <v>270.6591</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>297.8384</v>
+        <v>300.7098</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>327.68399999999997</v>
+        <v>330.7605</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>360.81120000000004</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>277.9287</v>
+        <v>234.5672</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>308.5386</v>
+        <v>261.84159999999997</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>339.1485</v>
+        <v>289.116</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>316.3904</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>270.6591</v>
+        <v>355.77400000000006</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>300.7098</v>
+        <v>392.372</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>330.7605</v>
+        <v>428.97</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>465.56800000000004</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>234.5672</v>
+        <v>414.4404</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>261.84159999999997</v>
+        <v>455.5512</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>289.116</v>
+        <v>496.66200000000003</v>
+      </c>
+      <c r="E43" t="n" s="0">
+        <v>537.7728</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>355.77400000000006</v>
+        <v>402.7976</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>392.372</v>
+        <v>443.01279999999997</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>428.97</v>
+        <v>483.22799999999995</v>
+      </c>
+      <c r="E44" t="n" s="0">
+        <v>523.4431999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>414.4404</v>
+        <v>470.12070000000006</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>455.5512</v>
+        <v>515.5146</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>496.66200000000003</v>
+        <v>560.9085</v>
+      </c>
+      <c r="E45" t="n" s="0">
+        <v>606.3024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>402.7976</v>
+        <v>489.427</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>443.01279999999997</v>
+        <v>536.306</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>483.22799999999995</v>
+        <v>583.1850000000001</v>
+      </c>
+      <c r="E46" t="n" s="0">
+        <v>630.0640000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>470.12070000000006</v>
+        <v>367.8354</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>515.5146</v>
+        <v>405.36119999999994</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>560.9085</v>
+        <v>442.88699999999994</v>
+      </c>
+      <c r="E47" t="n" s="0">
+        <v>480.4128</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>489.427</v>
+        <v>443.017</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>536.306</v>
+        <v>486.3259999999999</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>583.1850000000001</v>
+        <v>529.635</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>572.944</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>367.8354</v>
+        <v>446.59850000000006</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>405.36119999999994</v>
+        <v>490.183</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>442.88699999999994</v>
+        <v>533.7675</v>
+      </c>
+      <c r="E49" t="n" s="0">
+        <v>577.3520000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>443.017</v>
+        <v>403.39560000000006</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>486.3259999999999</v>
+        <v>443.65680000000003</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>529.635</v>
+        <v>483.918</v>
+      </c>
+      <c r="E50" t="n" s="0">
+        <v>524.1792</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>446.59850000000006</v>
+        <v>402.7976</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>490.183</v>
+        <v>443.01279999999997</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>533.7675</v>
+        <v>483.22799999999995</v>
+      </c>
+      <c r="E51" t="n" s="0">
+        <v>523.4431999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>403.39560000000006</v>
+        <v>405.14085</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>443.65680000000003</v>
+        <v>445.5363</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>483.918</v>
+        <v>485.93174999999997</v>
+      </c>
+      <c r="E52" t="n" s="0">
+        <v>526.3272</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>402.7976</v>
+        <v>439.8931</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>443.01279999999997</v>
+        <v>482.9618</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>483.22799999999995</v>
+        <v>526.0305000000001</v>
+      </c>
+      <c r="E53" t="n" s="0">
+        <v>569.0992</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>405.14085</v>
+        <v>395.333</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>445.5363</v>
+        <v>434.974</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>485.93174999999997</v>
+        <v>474.615</v>
+      </c>
+      <c r="E54" t="n" s="0">
+        <v>514.2560000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>439.8931</v>
+        <v>386.85699999999997</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>482.9618</v>
+        <v>425.84599999999995</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>526.0305000000001</v>
+        <v>464.835</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>503.824</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>395.333</v>
+        <v>398.48030000000006</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>434.974</v>
+        <v>438.3634</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>474.615</v>
+        <v>478.2465</v>
+      </c>
+      <c r="E56" t="n" s="0">
+        <v>518.1296</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>386.85699999999997</v>
+        <v>270.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>425.84599999999995</v>
+        <v>300.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>464.835</v>
+        <v>330.0</v>
+      </c>
+      <c r="E57" t="n" s="0">
+        <v>360.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>398.48030000000006</v>
+        <v>376.77029999999996</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>438.3634</v>
+        <v>414.98339999999996</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>478.2465</v>
+        <v>453.19649999999996</v>
+      </c>
+      <c r="E58" t="n" s="0">
+        <v>491.40959999999995</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>270.0</v>
+        <v>419.3999</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>300.0</v>
+        <v>460.8922</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>330.0</v>
+        <v>502.3845</v>
+      </c>
+      <c r="E59" t="n" s="0">
+        <v>543.8768</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>376.77029999999996</v>
+        <v>461.9372</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>414.98339999999996</v>
+        <v>506.7016</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>453.19649999999996</v>
+        <v>551.466</v>
+      </c>
+      <c r="E60" t="n" s="0">
+        <v>596.2304</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>419.3999</v>
+        <v>365.0339</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>460.8922</v>
+        <v>402.3442</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>502.3845</v>
+        <v>439.6545</v>
+      </c>
+      <c r="E61" t="n" s="0">
+        <v>476.9648</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>461.9372</v>
+        <v>334.4267</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>506.7016</v>
+        <v>369.38259999999997</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>551.466</v>
+        <v>404.3385</v>
+      </c>
+      <c r="E62" t="n" s="0">
+        <v>439.2944</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>365.0339</v>
+        <v>324.4141</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>402.3442</v>
+        <v>358.59979999999996</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>439.6545</v>
+        <v>392.7855</v>
+      </c>
+      <c r="E63" t="n" s="0">
+        <v>426.9712</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>334.4267</v>
+        <v>282.7166</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>369.38259999999997</v>
+        <v>313.6948</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>404.3385</v>
+        <v>344.673</v>
+      </c>
+      <c r="E64" t="n" s="0">
+        <v>375.6512</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>324.4141</v>
+        <v>287.7268</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>358.59979999999996</v>
+        <v>319.0904</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>392.7855</v>
+        <v>350.454</v>
+      </c>
+      <c r="E65" t="n" s="0">
+        <v>381.8176</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>282.7166</v>
+        <v>309.0624</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>313.6948</v>
+        <v>342.06719999999996</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>344.673</v>
+        <v>375.072</v>
+      </c>
+      <c r="E66" t="n" s="0">
+        <v>408.07680000000005</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>287.7268</v>
+        <v>328.8367</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>319.0904</v>
+        <v>363.3626</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>350.454</v>
+        <v>397.88849999999996</v>
+      </c>
+      <c r="E67" t="n" s="0">
+        <v>432.4144</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>309.0624</v>
+        <v>286.2162</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>342.06719999999996</v>
+        <v>317.4636</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>375.072</v>
+        <v>348.711</v>
+      </c>
+      <c r="E68" t="n" s="0">
+        <v>379.9584</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>328.8367</v>
+        <v>291.4786</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>363.3626</v>
+        <v>323.13079999999997</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>397.88849999999996</v>
+        <v>354.783</v>
+      </c>
+      <c r="E69" t="n" s="0">
+        <v>386.4352</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>286.2162</v>
+        <v>279.11690000000004</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>317.4636</v>
+        <v>309.8182</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>348.711</v>
+        <v>340.5195</v>
+      </c>
+      <c r="E70" t="n" s="0">
+        <v>371.22080000000005</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>291.4786</v>
+        <v>229.09940000000003</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>323.13079999999997</v>
+        <v>255.9532</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>354.783</v>
+        <v>282.807</v>
+      </c>
+      <c r="E71" t="n" s="0">
+        <v>309.66080000000005</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>279.11690000000004</v>
+        <v>342.163</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>309.8182</v>
+        <v>377.71399999999994</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>340.5195</v>
+        <v>413.265</v>
+      </c>
+      <c r="E72" t="n" s="0">
+        <v>448.81600000000003</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>229.09940000000003</v>
+        <v>299.56850000000003</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>255.9532</v>
+        <v>331.84299999999996</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>282.807</v>
+        <v>364.1175</v>
+      </c>
+      <c r="E73" t="n" s="0">
+        <v>396.39200000000005</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>342.163</v>
+        <v>450.98859999999996</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>377.71399999999994</v>
+        <v>494.91079999999994</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>413.265</v>
+        <v>538.833</v>
+      </c>
+      <c r="E74" t="n" s="0">
+        <v>582.7552</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>299.56850000000003</v>
+        <v>429.8506</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>331.84299999999996</v>
+        <v>472.1467999999999</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>364.1175</v>
+        <v>514.443</v>
+      </c>
+      <c r="E75" t="n" s="0">
+        <v>556.7392</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>450.98859999999996</v>
+        <v>523.9134</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>494.91079999999994</v>
+        <v>573.4451999999999</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>538.833</v>
+        <v>622.977</v>
+      </c>
+      <c r="E76" t="n" s="0">
+        <v>672.5088000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>429.8506</v>
+        <v>282.6139</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>472.1467999999999</v>
+        <v>313.5842</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>514.443</v>
+        <v>344.5545</v>
+      </c>
+      <c r="E77" t="n" s="0">
+        <v>375.5248</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>523.9134</v>
+        <v>478.62919999999997</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>573.4451999999999</v>
+        <v>524.6776</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>622.977</v>
+        <v>570.726</v>
+      </c>
+      <c r="E78" t="n" s="0">
+        <v>616.7744</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>282.6139</v>
+        <v>459.3008</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>313.5842</v>
+        <v>503.8623999999999</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>344.5545</v>
+        <v>548.424</v>
+      </c>
+      <c r="E79" t="n" s="0">
+        <v>592.9856</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>478.62919999999997</v>
+        <v>406.80160000000006</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>524.6776</v>
+        <v>447.32480000000004</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>570.726</v>
+        <v>487.84800000000007</v>
+      </c>
+      <c r="E80" t="n" s="0">
+        <v>528.3712</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>459.3008</v>
+        <v>406.70930000000004</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>503.8623999999999</v>
+        <v>447.2254</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>548.424</v>
+        <v>487.7415</v>
+      </c>
+      <c r="E81" t="n" s="0">
+        <v>528.2576</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>406.80160000000006</v>
+        <v>281.77930000000003</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>447.32480000000004</v>
+        <v>312.6854</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>487.84800000000007</v>
+        <v>343.5915</v>
+      </c>
+      <c r="E82" t="n" s="0">
+        <v>374.49760000000003</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>406.70930000000004</v>
+        <v>281.77930000000003</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>447.2254</v>
+        <v>312.6854</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>487.7415</v>
+        <v>343.5915</v>
+      </c>
+      <c r="E83" t="n" s="0">
+        <v>374.49760000000003</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>281.77930000000003</v>
+        <v>371.62360000000007</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>312.6854</v>
+        <v>409.4408</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>343.5915</v>
+        <v>447.25800000000004</v>
+      </c>
+      <c r="E84" t="n" s="0">
+        <v>485.07520000000005</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>281.77930000000003</v>
+        <v>366.5107</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>312.6854</v>
+        <v>403.93459999999993</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>343.5915</v>
+        <v>441.35849999999994</v>
+      </c>
+      <c r="E85" t="n" s="0">
+        <v>478.7824</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>371.62360000000007</v>
+        <v>366.616</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>409.4408</v>
+        <v>404.04799999999994</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>447.25800000000004</v>
+        <v>441.48</v>
+      </c>
+      <c r="E86" t="n" s="0">
+        <v>478.91200000000003</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>366.5107</v>
+        <v>376.14240000000007</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>403.93459999999993</v>
+        <v>414.3072</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>441.35849999999994</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>366.616</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>404.04799999999994</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>441.48</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>376.14240000000007</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>414.3072</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>452.47200000000004</v>
       </c>
+      <c r="E87" t="n" s="0">
+        <v>490.63680000000005</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D89"/>
+  <autoFilter ref="A1:E87"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -3399,678 +3598,695 @@
     <tabColor indexed="48"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="10.47265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.51171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.69921875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="21.0" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.47265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.234375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="14.51171875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="22.69921875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="21.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>243</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>245</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>247</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="K1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="L1" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="J1" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="K1" t="s" s="0">
+      <c r="M1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="N1" t="s" s="0">
         <v>249</v>
       </c>
-      <c r="L1" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="M1" t="s" s="0">
+      <c r="O1" t="s" s="0">
         <v>250</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B2" s="0"/>
       <c r="C2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E2" t="n" s="0">
+      <c r="F2" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G2" t="b" s="0">
+      <c r="G2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H2" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I2" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J2" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="b" s="0">
+      <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L2" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L2" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M2" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O2" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B3" s="0"/>
       <c r="C3" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E3" t="n" s="0">
+      <c r="F3" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G3" t="b" s="0">
+      <c r="G3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H3" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H3" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I3" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J3" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="b" s="0">
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L3" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L3" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M3" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O3" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B4" s="0"/>
       <c r="C4" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E4" t="n" s="0">
+      <c r="F4" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F4" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G4" t="b" s="0">
+      <c r="G4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H4" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H4" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I4" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="b" s="0">
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L4" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L4" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M4" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O4" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N4" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>126</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B5" s="0"/>
       <c r="C5" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E5" t="n" s="0">
+      <c r="F5" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G5" t="b" s="0">
+      <c r="G5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H5" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H5" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I5" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="b" s="0">
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L5" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L5" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M5" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O5" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B6" s="0"/>
+      <c r="C6" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E6" t="n" s="0">
+      <c r="F6" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G6" t="b" s="0">
+      <c r="G6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H6" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H6" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I6" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J6" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s" s="0">
-        <v>59</v>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L6" t="b" s="0">
+        <v>0</v>
       </c>
       <c r="M6" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O6" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N6" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B7" s="0"/>
       <c r="C7" t="s" s="0">
         <v>109</v>
       </c>
       <c r="D7" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E7" t="n" s="0">
+      <c r="F7" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G7" t="b" s="0">
+      <c r="G7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H7" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H7" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I7" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J7" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="b" s="0">
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L7" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L7" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M7" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O7" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N7" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>114</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B8" s="0"/>
       <c r="C8" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E8" t="n" s="0">
+      <c r="F8" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G8" t="b" s="0">
+      <c r="G8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H8" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I8" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J8" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="b" s="0">
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L8" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O8" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N8" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B9" s="0"/>
+      <c r="C9" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="E9" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="F9" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G9" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="M9" t="s" s="0">
+      <c r="N9" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O9" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N9" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B10" s="0"/>
       <c r="C10" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E10" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E10" t="n" s="0">
+      <c r="F10" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F10" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G10" t="b" s="0">
+      <c r="G10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H10" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H10" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I10" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J10" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K10" t="b" s="0">
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L10" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O10" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N10" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>128</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B11" s="0"/>
       <c r="C11" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E11" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E11" t="n" s="0">
+      <c r="F11" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F11" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G11" t="b" s="0">
+      <c r="G11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H11" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H11" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I11" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J11" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K11" t="b" s="0">
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L11" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O11" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N11" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>112</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B12" s="0"/>
       <c r="C12" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E12" t="n" s="0">
+      <c r="F12" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F12" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G12" t="b" s="0">
+      <c r="G12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H12" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H12" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I12" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J12" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K12" t="b" s="0">
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L12" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M12" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O12" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N12" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B13" s="0"/>
       <c r="C13" t="s" s="0">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E13" t="n" s="0">
+      <c r="F13" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F13" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G13" t="b" s="0">
+      <c r="G13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H13" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H13" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I13" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K13" t="b" s="0">
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L13" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M13" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O13" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N13" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B14" s="0"/>
       <c r="C14" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E14" t="n" s="0">
+        <v>122</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="F14" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F14" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G14" t="b" s="0">
+      <c r="G14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H14" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H14" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I14" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J14" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K14" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s" s="0">
-        <v>59</v>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="b" s="0">
+        <v>0</v>
       </c>
       <c r="M14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O14" t="s" s="0">
         <v>252</v>
-      </c>
-      <c r="N14" t="s" s="0">
-        <v>253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B15" s="0"/>
       <c r="C15" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E15" t="n" s="0">
+      <c r="F15" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="F15" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G15" t="b" s="0">
+      <c r="G15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H15" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="H15" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="I15" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="J15" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K15" t="b" s="0">
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="L15" t="s" s="0">
-        <v>59</v>
-      </c>
       <c r="M15" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="O15" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="N15" t="s" s="0">
-        <v>253</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -4095,53 +4311,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>255</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="F2" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="G2" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="F2" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="G2" t="s" s="0">
+      <c r="H2" t="s" s="0">
         <v>257</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>258</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>28</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>259</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>260</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>38261.0</v>
@@ -4150,13 +4366,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>28</v>
@@ -4165,7 +4381,7 @@
         <v>28</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>33147.0</v>
@@ -4174,13 +4390,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>28</v>
@@ -4189,7 +4405,7 @@
         <v>28</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>37530.0</v>
@@ -4198,13 +4414,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>28</v>
@@ -4213,7 +4429,7 @@
         <v>28</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>36100.0</v>
@@ -4222,22 +4438,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>28</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>36434.0</v>
@@ -4246,22 +4462,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>28</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>33512.0</v>
@@ -4270,13 +4486,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>28</v>
@@ -4285,7 +4501,7 @@
         <v>28</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>37653.0</v>
@@ -4294,22 +4510,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="F10" t="s" s="0">
         <v>261</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>262</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>43739.0</v>
@@ -4342,13 +4558,13 @@
         <v>4</v>
       </c>
       <c r="C1" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>263</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="E1" t="s" s="0">
         <v>264</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>265</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>13</v>
@@ -4360,7 +4576,7 @@
         <v>17</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J1" t="s" s="0">
         <v>19</v>
@@ -4409,7 +4625,7 @@
         <v>105.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>2.0</v>
@@ -4444,7 +4660,7 @@
         <v>101.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -4479,7 +4695,7 @@
         <v>102.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -4514,7 +4730,7 @@
         <v>103.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -4549,7 +4765,7 @@
         <v>104.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -4584,7 +4800,7 @@
         <v>106.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -4619,7 +4835,7 @@
         <v>107.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -4654,7 +4870,7 @@
         <v>108.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -4689,7 +4905,7 @@
         <v>109.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -4724,7 +4940,7 @@
         <v>201.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -4759,7 +4975,7 @@
         <v>202.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -4794,7 +5010,7 @@
         <v>203.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -4827,7 +5043,7 @@
         <v>204.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -4862,7 +5078,7 @@
         <v>205.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -4897,7 +5113,7 @@
         <v>206.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -4932,7 +5148,7 @@
         <v>207.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -4967,7 +5183,7 @@
         <v>208.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -5002,7 +5218,7 @@
         <v>209.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -5037,7 +5253,7 @@
         <v>210.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -5072,7 +5288,7 @@
         <v>211.0</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -5107,7 +5323,7 @@
         <v>301.0</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -5142,7 +5358,7 @@
         <v>302.0</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -5177,7 +5393,7 @@
         <v>303.0</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -5212,7 +5428,7 @@
         <v>304.0</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -5247,7 +5463,7 @@
         <v>305.0</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -5282,7 +5498,7 @@
         <v>401.0</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -5317,7 +5533,7 @@
         <v>501.0</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -5352,7 +5568,7 @@
         <v>502.0</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -5387,7 +5603,7 @@
         <v>503.0</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -5422,7 +5638,7 @@
         <v>504.0</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -5457,7 +5673,7 @@
         <v>601.0</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -5492,7 +5708,7 @@
         <v>602.0</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -5527,7 +5743,7 @@
         <v>603.0</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -5562,7 +5778,7 @@
         <v>604.0</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -5597,7 +5813,7 @@
         <v>605.0</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -5632,7 +5848,7 @@
         <v>606.0</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -5667,7 +5883,7 @@
         <v>607.0</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -5702,7 +5918,7 @@
         <v>608.0</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -5737,7 +5953,7 @@
         <v>609.0</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -5772,7 +5988,7 @@
         <v>610.0</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -5807,7 +6023,7 @@
         <v>611.0</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -5842,7 +6058,7 @@
         <v>612.0</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -5877,7 +6093,7 @@
         <v>701.0</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -5912,7 +6128,7 @@
         <v>702.0</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -5947,7 +6163,7 @@
         <v>703.0</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -5980,7 +6196,7 @@
         <v>704.0</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -6015,7 +6231,7 @@
         <v>705.0</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -6050,7 +6266,7 @@
         <v>706.0</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -6085,7 +6301,7 @@
         <v>707.0</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -6120,7 +6336,7 @@
         <v>708.0</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -6155,7 +6371,7 @@
         <v>801.0</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -6190,7 +6406,7 @@
         <v>901.0</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -6225,7 +6441,7 @@
         <v>1001.0</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -6260,7 +6476,7 @@
         <v>1002.0</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -6295,7 +6511,7 @@
         <v>1003.0</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -6348,58 +6564,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>30</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E1" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F1" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="G1" t="s" s="0">
         <v>322</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>323</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="I1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="J1" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="I1" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="J1" t="s" s="0">
+      <c r="K1" t="s" s="0">
         <v>325</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="L1" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="M1" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="N1" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="O1" t="s" s="0">
         <v>329</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="P1" t="s" s="0">
         <v>330</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>331</v>
       </c>
       <c r="Q1" t="s" s="0">
         <v>39</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S1" t="s" s="0">
         <v>38</v>
@@ -6428,7 +6644,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>30</v>
@@ -6440,19 +6656,19 @@
         <v>40</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="I1" t="s" s="0">
         <v>334</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>335</v>
       </c>
       <c r="J1" t="s" s="0">
         <v>39</v>
@@ -6489,10 +6705,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>30</v>
@@ -6501,67 +6717,67 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>40</v>
       </c>
       <c r="G1" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="H1" t="s" s="0">
         <v>338</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>339</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="K1" t="s" s="0">
         <v>341</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="L1" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="M1" t="s" s="0">
         <v>343</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="N1" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="O1" t="s" s="0">
         <v>345</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="P1" t="s" s="0">
         <v>346</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="Q1" t="s" s="0">
         <v>347</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="R1" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="S1" t="s" s="0">
         <v>349</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="T1" t="s" s="0">
         <v>350</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="U1" t="s" s="0">
         <v>351</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="V1" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="W1" t="s" s="0">
         <v>353</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="X1" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="Y1" t="s" s="0">
         <v>355</v>
-      </c>
-      <c r="Y1" t="s" s="0">
-        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -6591,22 +6807,22 @@
         <v>30</v>
       </c>
       <c r="B1" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>357</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>359</v>
-      </c>
       <c r="E1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1" t="s" s="0">
         <v>40</v>
@@ -6640,25 +6856,25 @@
         <v>30</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>357</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="E1" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="E1" t="s" s="0">
-        <v>359</v>
-      </c>
       <c r="F1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>40</v>
@@ -6687,53 +6903,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>361</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>362</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>363</v>
       </c>
       <c r="D1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45811.114405706016</v>
+        <v>45998.557844953706</v>
       </c>
       <c r="B2" t="s" s="6">
+        <v>364</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>365</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="D2" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>366</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>367</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45811.114405706016</v>
+        <v>45998.557844953706</v>
       </c>
       <c r="B3" t="s" s="6">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>365</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>366</v>
-      </c>
       <c r="D3" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6847,16 +7063,17 @@
     <tabColor indexed="42"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="15.0" outlineLevelCol="1"/>
   <cols>
-    <col min="5" max="6" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
-    <col min="7" max="7" collapsed="true" width="8.0" customWidth="false"/>
-    <col min="9" max="9" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
-    <col min="10" max="10" collapsed="true" width="8.0" customWidth="false"/>
-    <col min="12" max="12" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
-    <col min="13" max="13" collapsed="true" width="8.0" customWidth="false"/>
-    <col min="2" max="2" width="22.57421875" customWidth="true" bestFit="true"/>
+    <col min="7" max="8" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
+    <col min="9" max="9" collapsed="true" width="8.0" customWidth="false"/>
+    <col min="11" max="11" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
+    <col min="12" max="12" collapsed="true" width="8.0" customWidth="false"/>
+    <col min="14" max="14" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
+    <col min="15" max="15" collapsed="true" width="8.0" customWidth="false"/>
+    <col min="3" max="3" width="22.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="12.046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6866,31 +7083,31 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>45</v>
-      </c>
       <c r="G2" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="I2" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>47</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>48</v>
@@ -6911,35 +7128,39 @@
         <v>53</v>
       </c>
       <c r="P2" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="R2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="Q2" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="R2" t="s" s="0">
+      <c r="S2" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="T2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="S2" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="T2" t="s" s="0">
-        <v>56</v>
+      <c r="U2" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="C3" s="0"/>
-      <c r="D3" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B3" s="0"/>
+      <c r="C3" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E3" s="0"/>
       <c r="F3" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -6947,55 +7168,59 @@
         <v>0.0</v>
       </c>
       <c r="H3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J3" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I3" t="n" s="0">
+      <c r="K3" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J3" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L3" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O3" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P3" t="n" s="5">
+      <c r="P3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R3" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q3" s="0"/>
-      <c r="R3" s="0"/>
-      <c r="S3" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T3" t="s" s="0">
-        <v>59</v>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+      <c r="U3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V3" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B4" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B4" s="0"/>
+      <c r="C4" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="C4" s="0"/>
-      <c r="D4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E4" t="n" s="0">
-        <v>0.0</v>
-      </c>
+      <c r="E4" s="0"/>
       <c r="F4" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7003,111 +7228,119 @@
         <v>0.0</v>
       </c>
       <c r="H4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I4" t="n" s="0">
+      <c r="K4" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L4" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O4" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P4" t="n" s="5">
+      <c r="P4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R4" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q4" s="0"/>
-      <c r="R4" s="0"/>
-      <c r="S4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T4" t="s" s="0">
-        <v>59</v>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
+      <c r="U4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V4" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B5" s="0"/>
+      <c r="C5" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E5" s="0"/>
+      <c r="F5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R5" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
+      <c r="U5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V5" t="s" s="0">
         <v>62</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="C5" s="0"/>
-      <c r="D5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H5" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="I5" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="J5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="L5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="M5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="N5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="O5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="P5" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="Q5" s="0"/>
-      <c r="R5" s="0"/>
-      <c r="S5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T5" t="s" s="0">
-        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="C6" s="0"/>
-      <c r="D6" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E6" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B6" s="0"/>
+      <c r="C6" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E6" s="0"/>
       <c r="F6" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7115,55 +7348,59 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J6" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I6" t="n" s="0">
+      <c r="K6" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J6" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L6" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O6" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P6" t="n" s="5">
+      <c r="P6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R6" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q6" s="0"/>
-      <c r="R6" s="0"/>
-      <c r="S6" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T6" t="s" s="0">
-        <v>59</v>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
+      <c r="U6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V6" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="C7" s="0"/>
-      <c r="D7" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E7" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B7" s="0"/>
+      <c r="C7" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E7" s="0"/>
       <c r="F7" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7171,55 +7408,59 @@
         <v>0.0</v>
       </c>
       <c r="H7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J7" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I7" t="n" s="0">
+      <c r="K7" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J7" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L7" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O7" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P7" t="n" s="5">
+      <c r="P7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R7" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q7" s="0"/>
-      <c r="R7" s="0"/>
-      <c r="S7" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T7" t="s" s="0">
-        <v>59</v>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+      <c r="U7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V7" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="C8" s="0"/>
-      <c r="D8" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E8" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B8" s="0"/>
+      <c r="C8" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E8" s="0"/>
       <c r="F8" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7227,55 +7468,59 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I8" t="n" s="0">
+      <c r="K8" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J8" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L8" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O8" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P8" t="n" s="5">
+      <c r="P8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R8" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T8" t="s" s="0">
-        <v>59</v>
+      <c r="S8" s="0"/>
+      <c r="T8" s="0"/>
+      <c r="U8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V8" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="C9" s="0"/>
-      <c r="D9" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E9" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B9" s="0"/>
+      <c r="C9" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E9" s="0"/>
       <c r="F9" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7283,55 +7528,59 @@
         <v>0.0</v>
       </c>
       <c r="H9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I9" t="n" s="0">
+      <c r="K9" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J9" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L9" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O9" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P9" t="n" s="5">
+      <c r="P9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R9" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q9" s="0"/>
-      <c r="R9" s="0"/>
-      <c r="S9" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T9" t="s" s="0">
-        <v>59</v>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
+      <c r="U9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V9" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="C10" s="0"/>
-      <c r="D10" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E10" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B10" s="0"/>
+      <c r="C10" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E10" s="0"/>
       <c r="F10" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7339,55 +7588,59 @@
         <v>0.0</v>
       </c>
       <c r="H10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I10" t="n" s="0">
+      <c r="K10" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J10" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K10" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L10" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O10" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P10" t="n" s="5">
+      <c r="P10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R10" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q10" s="0"/>
-      <c r="R10" s="0"/>
-      <c r="S10" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T10" t="s" s="0">
-        <v>59</v>
+      <c r="S10" s="0"/>
+      <c r="T10" s="0"/>
+      <c r="U10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V10" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="C11" s="0"/>
-      <c r="D11" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E11" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B11" s="0"/>
+      <c r="C11" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E11" s="0"/>
       <c r="F11" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7395,55 +7648,59 @@
         <v>0.0</v>
       </c>
       <c r="H11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I11" t="n" s="0">
+      <c r="K11" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J11" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K11" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L11" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O11" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P11" t="n" s="5">
+      <c r="P11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R11" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T11" t="s" s="0">
-        <v>59</v>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
+      <c r="U11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V11" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="C12" s="0"/>
-      <c r="D12" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E12" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B12" s="0"/>
+      <c r="C12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E12" s="0"/>
       <c r="F12" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7451,55 +7708,59 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I12" t="n" s="0">
+      <c r="K12" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J12" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K12" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L12" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O12" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P12" t="n" s="5">
+      <c r="P12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R12" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
-      <c r="S12" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T12" t="s" s="0">
-        <v>59</v>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+      <c r="U12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V12" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="C13" s="0"/>
-      <c r="D13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E13" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B13" s="0"/>
+      <c r="C13" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E13" s="0"/>
       <c r="F13" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7507,55 +7768,59 @@
         <v>0.0</v>
       </c>
       <c r="H13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I13" t="n" s="0">
+      <c r="K13" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K13" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L13" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O13" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P13" t="n" s="5">
+      <c r="P13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R13" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
-      <c r="S13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T13" t="s" s="0">
-        <v>59</v>
+      <c r="S13" s="0"/>
+      <c r="T13" s="0"/>
+      <c r="U13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V13" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="C14" s="0"/>
-      <c r="D14" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E14" t="n" s="0">
-        <v>0.0</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B14" s="0"/>
+      <c r="C14" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E14" s="0"/>
       <c r="F14" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -7563,43 +7828,49 @@
         <v>0.0</v>
       </c>
       <c r="H14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="I14" t="n" s="0">
+      <c r="K14" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="J14" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="K14" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="L14" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M14" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N14" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O14" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="P14" t="n" s="5">
+      <c r="P14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Q14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="R14" t="n" s="5">
         <v>3.0</v>
       </c>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
-      <c r="S14" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="T14" t="s" s="0">
-        <v>59</v>
+      <c r="S14" s="0"/>
+      <c r="T14" s="0"/>
+      <c r="U14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V14" t="s" s="0">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T14"/>
+  <autoFilter ref="A2:V14"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -7612,10 +7883,11 @@
     <tabColor indexed="42"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="5.7734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="5.7734375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.59765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7625,35 +7897,41 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I2"/>
+  <autoFilter ref="A2:K2"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -7666,16 +7944,16 @@
     <tabColor indexed="42"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="5.7734375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="8.0" customWidth="true"/>
-    <col min="13" max="13" width="8.0" customWidth="true"/>
+    <col min="3" max="3" width="5.7734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.0" customWidth="true"/>
     <col min="14" max="14" width="8.0" customWidth="true"/>
     <col min="15" max="15" width="8.0" customWidth="true"/>
     <col min="16" max="16" width="8.0" customWidth="true"/>
     <col min="17" max="17" width="8.0" customWidth="true"/>
+    <col min="18" max="18" width="8.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7685,20 +7963,23 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>88</v>
+        <v>45</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:E2"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -7711,1847 +7992,1906 @@
     <tabColor indexed="11"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="10.47265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.51171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.6171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.47265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.234375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="14.51171875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="10.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B2" s="0"/>
       <c r="C2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E2" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F2" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G2" s="0"/>
+      <c r="G2" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H2" s="0"/>
       <c r="I2" s="0"/>
-      <c r="J2" t="n" s="0">
+      <c r="J2" s="0"/>
+      <c r="K2" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K2" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B3" s="0"/>
       <c r="C3" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E3" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F3" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G3" s="0"/>
+      <c r="G3" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H3" s="0"/>
       <c r="I3" s="0"/>
-      <c r="J3" t="n" s="0">
+      <c r="J3" s="0"/>
+      <c r="K3" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K3" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B4" s="0"/>
       <c r="C4" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E4" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F4" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G4" s="0"/>
+      <c r="G4" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H4" s="0"/>
       <c r="I4" s="0"/>
-      <c r="J4" t="n" s="0">
+      <c r="J4" s="0"/>
+      <c r="K4" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K4" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B5" s="0"/>
       <c r="C5" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E5" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F5" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G5" s="0"/>
+      <c r="G5" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H5" s="0"/>
       <c r="I5" s="0"/>
-      <c r="J5" t="n" s="0">
+      <c r="J5" s="0"/>
+      <c r="K5" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K5" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B6" s="0"/>
       <c r="C6" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E6" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F6" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G6" s="0"/>
+      <c r="G6" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H6" s="0"/>
       <c r="I6" s="0"/>
-      <c r="J6" t="n" s="0">
+      <c r="J6" s="0"/>
+      <c r="K6" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K6" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B7" s="0"/>
       <c r="C7" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E7" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F7" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G7" s="0"/>
+      <c r="G7" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H7" s="0"/>
       <c r="I7" s="0"/>
-      <c r="J7" t="n" s="0">
+      <c r="J7" s="0"/>
+      <c r="K7" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K7" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B8" s="0"/>
       <c r="C8" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E8" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F8" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G8" s="0"/>
+      <c r="G8" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H8" s="0"/>
       <c r="I8" s="0"/>
-      <c r="J8" t="n" s="0">
+      <c r="J8" s="0"/>
+      <c r="K8" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K8" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>103</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B9" s="0"/>
       <c r="C9" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E9" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F9" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G9" s="0"/>
+      <c r="G9" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H9" s="0"/>
       <c r="I9" s="0"/>
-      <c r="J9" t="n" s="0">
+      <c r="J9" s="0"/>
+      <c r="K9" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K9" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>105</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B10" s="0"/>
       <c r="C10" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E10" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E10" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F10" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G10" s="0"/>
+      <c r="G10" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H10" s="0"/>
       <c r="I10" s="0"/>
-      <c r="J10" t="n" s="0">
+      <c r="J10" s="0"/>
+      <c r="K10" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K10" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>105</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B11" s="0"/>
       <c r="C11" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E11" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F11" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G11" s="0"/>
+      <c r="G11" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H11" s="0"/>
       <c r="I11" s="0"/>
-      <c r="J11" t="n" s="0">
+      <c r="J11" s="0"/>
+      <c r="K11" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K11" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>105</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B12" s="0"/>
       <c r="C12" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E12" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F12" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G12" s="0"/>
+      <c r="G12" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H12" s="0"/>
       <c r="I12" s="0"/>
-      <c r="J12" t="n" s="0">
+      <c r="J12" s="0"/>
+      <c r="K12" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K12" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>105</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B13" s="0"/>
       <c r="C13" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E13" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F13" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G13" s="0"/>
+      <c r="G13" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H13" s="0"/>
       <c r="I13" s="0"/>
-      <c r="J13" t="n" s="0">
+      <c r="J13" s="0"/>
+      <c r="K13" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K13" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B14" s="0"/>
       <c r="C14" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E14" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F14" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G14" s="0"/>
+      <c r="G14" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H14" s="0"/>
       <c r="I14" s="0"/>
-      <c r="J14" t="n" s="0">
+      <c r="J14" s="0"/>
+      <c r="K14" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K14" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B15" s="0"/>
       <c r="C15" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E15" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F15" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G15" s="0"/>
+      <c r="G15" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" t="n" s="0">
+      <c r="J15" s="0"/>
+      <c r="K15" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K15" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B16" s="0"/>
       <c r="C16" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E16" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F16" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G16" s="0"/>
+      <c r="G16" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" t="n" s="0">
+      <c r="J16" s="0"/>
+      <c r="K16" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K16" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B17" s="0"/>
       <c r="C17" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E17" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F17" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G17" s="0"/>
+      <c r="G17" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H17" s="0"/>
       <c r="I17" s="0"/>
-      <c r="J17" t="n" s="0">
+      <c r="J17" s="0"/>
+      <c r="K17" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K17" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B18" s="0"/>
       <c r="C18" t="s" s="0">
         <v>109</v>
       </c>
       <c r="D18" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E18" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F18" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G18" s="0"/>
+      <c r="G18" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H18" s="0"/>
       <c r="I18" s="0"/>
-      <c r="J18" t="n" s="0">
+      <c r="J18" s="0"/>
+      <c r="K18" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K18" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L18" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B19" s="0"/>
       <c r="C19" t="s" s="0">
         <v>109</v>
       </c>
       <c r="D19" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E19" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E19" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F19" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G19" s="0"/>
+      <c r="G19" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H19" s="0"/>
       <c r="I19" s="0"/>
-      <c r="J19" t="n" s="0">
+      <c r="J19" s="0"/>
+      <c r="K19" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K19" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B20" s="0"/>
       <c r="C20" t="s" s="0">
         <v>109</v>
       </c>
       <c r="D20" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E20" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E20" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F20" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G20" s="0"/>
+      <c r="G20" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H20" s="0"/>
       <c r="I20" s="0"/>
-      <c r="J20" t="n" s="0">
+      <c r="J20" s="0"/>
+      <c r="K20" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K20" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>107</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B21" s="0"/>
       <c r="C21" t="s" s="0">
         <v>109</v>
       </c>
       <c r="D21" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E21" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F21" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G21" s="0"/>
+      <c r="G21" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" t="n" s="0">
+      <c r="J21" s="0"/>
+      <c r="K21" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K21" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B22" s="0"/>
       <c r="C22" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E22" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E22" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F22" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G22" s="0"/>
+      <c r="G22" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" t="n" s="0">
+      <c r="J22" s="0"/>
+      <c r="K22" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K22" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B23" s="0"/>
       <c r="C23" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E23" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F23" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G23" s="0"/>
+      <c r="G23" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H23" s="0"/>
       <c r="I23" s="0"/>
-      <c r="J23" t="n" s="0">
+      <c r="J23" s="0"/>
+      <c r="K23" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K23" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B24" s="0"/>
       <c r="C24" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E24" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E24" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F24" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G24" s="0"/>
+      <c r="G24" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H24" s="0"/>
       <c r="I24" s="0"/>
-      <c r="J24" t="n" s="0">
+      <c r="J24" s="0"/>
+      <c r="K24" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K24" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B25" s="0"/>
       <c r="C25" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E25" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F25" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G25" s="0"/>
+      <c r="G25" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H25" s="0"/>
       <c r="I25" s="0"/>
-      <c r="J25" t="n" s="0">
+      <c r="J25" s="0"/>
+      <c r="K25" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K25" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>112</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B26" s="0"/>
       <c r="C26" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E26" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E26" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F26" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G26" s="0"/>
+      <c r="G26" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H26" s="0"/>
       <c r="I26" s="0"/>
-      <c r="J26" t="n" s="0">
+      <c r="J26" s="0"/>
+      <c r="K26" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K26" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>112</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B27" s="0"/>
       <c r="C27" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E27" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E27" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F27" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G27" s="0"/>
+      <c r="G27" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H27" s="0"/>
       <c r="I27" s="0"/>
-      <c r="J27" t="n" s="0">
+      <c r="J27" s="0"/>
+      <c r="K27" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K27" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>112</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B28" s="0"/>
       <c r="C28" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E28" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E28" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F28" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G28" s="0"/>
+      <c r="G28" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H28" s="0"/>
       <c r="I28" s="0"/>
-      <c r="J28" t="n" s="0">
+      <c r="J28" s="0"/>
+      <c r="K28" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K28" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>112</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B29" s="0"/>
       <c r="C29" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E29" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E29" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F29" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G29" s="0"/>
+      <c r="G29" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H29" s="0"/>
       <c r="I29" s="0"/>
-      <c r="J29" t="n" s="0">
+      <c r="J29" s="0"/>
+      <c r="K29" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K29" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L29" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>114</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B30" s="0"/>
       <c r="C30" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E30" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E30" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F30" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G30" s="0"/>
+      <c r="G30" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H30" s="0"/>
       <c r="I30" s="0"/>
-      <c r="J30" t="n" s="0">
+      <c r="J30" s="0"/>
+      <c r="K30" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K30" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L30" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>114</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B31" s="0"/>
       <c r="C31" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E31" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F31" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G31" s="0"/>
+      <c r="G31" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H31" s="0"/>
       <c r="I31" s="0"/>
-      <c r="J31" t="n" s="0">
+      <c r="J31" s="0"/>
+      <c r="K31" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K31" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L31" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>114</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B32" s="0"/>
       <c r="C32" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E32" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E32" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F32" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G32" s="0"/>
+      <c r="G32" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H32" s="0"/>
       <c r="I32" s="0"/>
-      <c r="J32" t="n" s="0">
+      <c r="J32" s="0"/>
+      <c r="K32" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K32" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L32" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>114</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B33" s="0"/>
       <c r="C33" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E33" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E33" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F33" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G33" s="0"/>
+      <c r="G33" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H33" s="0"/>
       <c r="I33" s="0"/>
-      <c r="J33" t="n" s="0">
+      <c r="J33" s="0"/>
+      <c r="K33" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K33" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L33" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M33" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B34" s="0"/>
       <c r="C34" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E34" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E34" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F34" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G34" s="0"/>
+      <c r="G34" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H34" s="0"/>
       <c r="I34" s="0"/>
-      <c r="J34" t="n" s="0">
+      <c r="J34" s="0"/>
+      <c r="K34" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K34" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L34" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M34" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B35" s="0"/>
       <c r="C35" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E35" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E35" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F35" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G35" s="0"/>
+      <c r="G35" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H35" s="0"/>
       <c r="I35" s="0"/>
-      <c r="J35" t="n" s="0">
+      <c r="J35" s="0"/>
+      <c r="K35" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K35" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L35" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M35" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B36" s="0"/>
       <c r="C36" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E36" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E36" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F36" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G36" s="0"/>
+      <c r="G36" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H36" s="0"/>
       <c r="I36" s="0"/>
-      <c r="J36" t="n" s="0">
+      <c r="J36" s="0"/>
+      <c r="K36" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K36" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L36" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M36" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>116</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B37" s="0"/>
       <c r="C37" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E37" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E37" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F37" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G37" s="0"/>
+      <c r="G37" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H37" s="0"/>
       <c r="I37" s="0"/>
-      <c r="J37" t="n" s="0">
+      <c r="J37" s="0"/>
+      <c r="K37" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K37" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L37" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B38" s="0"/>
       <c r="C38" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E38" t="n" s="0">
-        <v>1.0</v>
+        <v>122</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="F38" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G38" s="0"/>
+      <c r="G38" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H38" s="0"/>
       <c r="I38" s="0"/>
-      <c r="J38" t="n" s="0">
+      <c r="J38" s="0"/>
+      <c r="K38" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K38" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L38" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M38" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B39" s="0"/>
       <c r="C39" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E39" t="n" s="0">
-        <v>1.0</v>
+        <v>122</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="F39" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G39" s="0"/>
+      <c r="G39" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H39" s="0"/>
       <c r="I39" s="0"/>
-      <c r="J39" t="n" s="0">
+      <c r="J39" s="0"/>
+      <c r="K39" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K39" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L39" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B40" s="0"/>
       <c r="C40" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E40" t="n" s="0">
-        <v>1.0</v>
+        <v>122</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="F40" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G40" s="0"/>
+      <c r="G40" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H40" s="0"/>
       <c r="I40" s="0"/>
-      <c r="J40" t="n" s="0">
+      <c r="J40" s="0"/>
+      <c r="K40" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K40" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L40" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B41" s="0"/>
       <c r="C41" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E41" t="n" s="0">
-        <v>1.0</v>
+        <v>122</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="F41" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G41" s="0"/>
+      <c r="G41" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H41" s="0"/>
       <c r="I41" s="0"/>
-      <c r="J41" t="n" s="0">
+      <c r="J41" s="0"/>
+      <c r="K41" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K41" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L41" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M41" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B42" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B42" s="0"/>
+      <c r="C42" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E42" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C42" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D42" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E42" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F42" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G42" s="0"/>
+      <c r="G42" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H42" s="0"/>
       <c r="I42" s="0"/>
-      <c r="J42" t="n" s="0">
+      <c r="J42" s="0"/>
+      <c r="K42" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K42" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L42" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B43" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B43" s="0"/>
+      <c r="C43" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E43" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C43" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E43" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F43" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G43" s="0"/>
+      <c r="G43" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H43" s="0"/>
       <c r="I43" s="0"/>
-      <c r="J43" t="n" s="0">
+      <c r="J43" s="0"/>
+      <c r="K43" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K43" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L43" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B44" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B44" s="0"/>
+      <c r="C44" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E44" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C44" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E44" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F44" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G44" s="0"/>
+      <c r="G44" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H44" s="0"/>
       <c r="I44" s="0"/>
-      <c r="J44" t="n" s="0">
+      <c r="J44" s="0"/>
+      <c r="K44" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K44" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L44" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M44" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B45" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B45" s="0"/>
+      <c r="C45" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E45" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C45" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E45" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F45" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G45" s="0"/>
+      <c r="G45" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H45" s="0"/>
       <c r="I45" s="0"/>
-      <c r="J45" t="n" s="0">
+      <c r="J45" s="0"/>
+      <c r="K45" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K45" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L45" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M45" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B46" s="0"/>
       <c r="C46" t="s" s="0">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E46" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E46" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F46" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G46" s="0"/>
+      <c r="G46" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H46" s="0"/>
       <c r="I46" s="0"/>
-      <c r="J46" t="n" s="0">
+      <c r="J46" s="0"/>
+      <c r="K46" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K46" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L46" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M46" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B47" s="0"/>
       <c r="C47" t="s" s="0">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E47" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E47" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F47" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G47" s="0"/>
+      <c r="G47" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H47" s="0"/>
       <c r="I47" s="0"/>
-      <c r="J47" t="n" s="0">
+      <c r="J47" s="0"/>
+      <c r="K47" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K47" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L47" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M47" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B48" s="0"/>
       <c r="C48" t="s" s="0">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E48" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E48" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F48" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G48" s="0"/>
+      <c r="G48" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H48" s="0"/>
       <c r="I48" s="0"/>
-      <c r="J48" t="n" s="0">
+      <c r="J48" s="0"/>
+      <c r="K48" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K48" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L48" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M48" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B49" s="0"/>
       <c r="C49" t="s" s="0">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E49" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E49" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F49" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G49" s="0"/>
+      <c r="G49" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H49" s="0"/>
       <c r="I49" s="0"/>
-      <c r="J49" t="n" s="0">
+      <c r="J49" s="0"/>
+      <c r="K49" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K49" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L49" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M49" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>126</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B50" s="0"/>
       <c r="C50" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E50" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E50" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F50" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G50" s="0"/>
+      <c r="G50" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H50" s="0"/>
       <c r="I50" s="0"/>
-      <c r="J50" t="n" s="0">
+      <c r="J50" s="0"/>
+      <c r="K50" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K50" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L50" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M50" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>126</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B51" s="0"/>
       <c r="C51" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E51" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E51" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F51" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G51" s="0"/>
+      <c r="G51" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H51" s="0"/>
       <c r="I51" s="0"/>
-      <c r="J51" t="n" s="0">
+      <c r="J51" s="0"/>
+      <c r="K51" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K51" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L51" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M51" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>126</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B52" s="0"/>
       <c r="C52" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E52" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E52" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F52" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G52" s="0"/>
+      <c r="G52" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H52" s="0"/>
       <c r="I52" s="0"/>
-      <c r="J52" t="n" s="0">
+      <c r="J52" s="0"/>
+      <c r="K52" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K52" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L52" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M52" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>126</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B53" s="0"/>
       <c r="C53" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D53" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E53" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E53" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F53" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G53" s="0"/>
+      <c r="G53" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H53" s="0"/>
       <c r="I53" s="0"/>
-      <c r="J53" t="n" s="0">
+      <c r="J53" s="0"/>
+      <c r="K53" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K53" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L53" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>128</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B54" s="0"/>
       <c r="C54" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E54" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E54" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F54" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G54" s="0"/>
+      <c r="G54" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H54" s="0"/>
       <c r="I54" s="0"/>
-      <c r="J54" t="n" s="0">
+      <c r="J54" s="0"/>
+      <c r="K54" t="n" s="0">
         <v>2022.0</v>
       </c>
-      <c r="K54" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L54" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>128</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B55" s="0"/>
       <c r="C55" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E55" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E55" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F55" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G55" s="0"/>
+      <c r="G55" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H55" s="0"/>
       <c r="I55" s="0"/>
-      <c r="J55" t="n" s="0">
+      <c r="J55" s="0"/>
+      <c r="K55" t="n" s="0">
         <v>2023.0</v>
       </c>
-      <c r="K55" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L55" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>128</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B56" s="0"/>
       <c r="C56" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E56" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E56" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F56" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G56" s="0"/>
+      <c r="G56" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H56" s="0"/>
       <c r="I56" s="0"/>
-      <c r="J56" t="n" s="0">
+      <c r="J56" s="0"/>
+      <c r="K56" t="n" s="0">
         <v>2024.0</v>
       </c>
-      <c r="K56" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L56" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>128</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B57" s="0"/>
       <c r="C57" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="E57" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E57" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F57" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G57" s="0"/>
+      <c r="G57" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="H57" s="0"/>
       <c r="I57" s="0"/>
-      <c r="J57" t="n" s="0">
+      <c r="J57" s="0"/>
+      <c r="K57" t="n" s="0">
         <v>2025.0</v>
       </c>
-      <c r="K57" t="b" s="0">
-        <v>0</v>
-      </c>
       <c r="L57" t="b" s="0">
         <v>0</v>
       </c>
+      <c r="M57" t="b" s="0">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L57"/>
+  <autoFilter ref="A1:M57"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -9564,41 +9904,41 @@
     <tabColor indexed="11"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="15.0" outlineLevelCol="1"/>
   <cols>
-    <col min="8" max="19" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
-    <col min="20" max="20" collapsed="true" width="22.1640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="4.171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="8.2265625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="4.8203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.6640625" customWidth="true" bestFit="true"/>
+    <col min="10" max="22" outlineLevel="1" hidden="true" width="8.0" customWidth="false"/>
+    <col min="23" max="23" collapsed="true" width="22.1640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="4.171875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="8.2265625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.8203125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="17.6640625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>132</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>133</v>
@@ -9613,38 +9953,47 @@
         <v>136</v>
       </c>
       <c r="M1" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="O1" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="N1" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>138</v>
-      </c>
       <c r="P1" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="R1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="S1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="T1" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="U1" t="s" s="0">
         <v>39</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>140</v>
       </c>
       <c r="V1" t="s" s="0">
         <v>141</v>
       </c>
+      <c r="W1" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V1"/>
+  <autoFilter ref="A1:Y1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
@@ -9657,45 +10006,48 @@
     <tabColor indexed="42"/>
     <outlinePr summaryRight="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="5.7734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="5.7734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H2"/>
+  <autoFilter ref="A2:I2"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
